--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N101_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N101_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>44.72501678572814</v>
+        <v>7.267815227680822</v>
       </c>
       <c r="D2" t="n">
-        <v>44.37181098370685</v>
+        <v>7.210419284852364</v>
       </c>
       <c r="E2" t="n">
-        <v>13.4486879396411</v>
+        <v>2.185411790191678</v>
       </c>
       <c r="F2" t="n">
-        <v>13.83622691212101</v>
+        <v>2.248386873219664</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.95512746300935</v>
+        <v>8.605208212739019</v>
       </c>
       <c r="D3" t="n">
-        <v>53.23690628449612</v>
+        <v>8.65099727123062</v>
       </c>
       <c r="E3" t="n">
-        <v>13.4486879396411</v>
+        <v>2.185411790191678</v>
       </c>
       <c r="F3" t="n">
-        <v>13.83622691212101</v>
+        <v>2.248386873219664</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.74271743883117</v>
+        <v>5.970691583810066</v>
       </c>
       <c r="D4" t="n">
-        <v>35.94931819277075</v>
+        <v>5.841764206325246</v>
       </c>
       <c r="E4" t="n">
-        <v>13.4486879396411</v>
+        <v>2.185411790191678</v>
       </c>
       <c r="F4" t="n">
-        <v>13.83622691212101</v>
+        <v>2.248386873219664</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>65.35770982249421</v>
+        <v>10.62062784615531</v>
       </c>
       <c r="D5" t="n">
-        <v>66.040378348223</v>
+        <v>10.73156148158624</v>
       </c>
       <c r="E5" t="n">
-        <v>13.4486879396411</v>
+        <v>2.185411790191678</v>
       </c>
       <c r="F5" t="n">
-        <v>13.83622691212101</v>
+        <v>2.248386873219664</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>45.78170261136396</v>
+        <v>7.439526674346644</v>
       </c>
       <c r="D6" t="n">
-        <v>44.90536169905309</v>
+        <v>7.297121276096127</v>
       </c>
       <c r="E6" t="n">
-        <v>13.4486879396411</v>
+        <v>2.185411790191678</v>
       </c>
       <c r="F6" t="n">
-        <v>13.83622691212101</v>
+        <v>2.248386873219664</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.76634266937683</v>
+        <v>3.537030683773735</v>
       </c>
       <c r="D7" t="n">
-        <v>21.36465651965909</v>
+        <v>3.471756684444602</v>
       </c>
       <c r="E7" t="n">
-        <v>13.4486879396411</v>
+        <v>2.185411790191678</v>
       </c>
       <c r="F7" t="n">
-        <v>13.83622691212101</v>
+        <v>2.248386873219664</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
